--- a/系统集成项目管理工程师/10大管理过程(输入-输出-工具-技术)汇总表.xlsx
+++ b/系统集成项目管理工程师/10大管理过程(输入-输出-工具-技术)汇总表.xlsx
@@ -1,33 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AngkorW\Desktop\RuanKao\系统集成项目管理工程师\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RuanKao\系统集成项目管理工程师\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD9247C-4CB7-4EC3-BAF6-343AA3CA824A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
-    <sheet name="1-整体管理" sheetId="1" r:id="rId1"/>
-    <sheet name="2-范围管理" sheetId="2" r:id="rId2"/>
-    <sheet name="3-进度管理" sheetId="3" r:id="rId3"/>
-    <sheet name="4-成本管理" sheetId="4" r:id="rId4"/>
-    <sheet name="5-质量管理" sheetId="5" r:id="rId5"/>
-    <sheet name="6-人力资源管理" sheetId="6" r:id="rId6"/>
-    <sheet name="7-沟通和项目干系人管理" sheetId="7" r:id="rId7"/>
-    <sheet name="8-项目干系人管理" sheetId="8" r:id="rId8"/>
-    <sheet name="9-风险管理" sheetId="9" r:id="rId9"/>
-    <sheet name="10-采购管理" sheetId="10" r:id="rId10"/>
-    <sheet name="Tips" sheetId="11" r:id="rId11"/>
-    <sheet name="5大过程组" sheetId="13" r:id="rId12"/>
+    <sheet name="5大过程组" sheetId="13" r:id="rId1"/>
+    <sheet name="1-整体管理" sheetId="1" r:id="rId2"/>
+    <sheet name="2-范围管理" sheetId="2" r:id="rId3"/>
+    <sheet name="3-进度管理" sheetId="3" r:id="rId4"/>
+    <sheet name="4-成本管理" sheetId="4" r:id="rId5"/>
+    <sheet name="5-质量管理" sheetId="5" r:id="rId6"/>
+    <sheet name="6-人力资源管理" sheetId="6" r:id="rId7"/>
+    <sheet name="7-沟通和项目干系人管理" sheetId="7" r:id="rId8"/>
+    <sheet name="8-项目干系人管理" sheetId="8" r:id="rId9"/>
+    <sheet name="9-风险管理" sheetId="9" r:id="rId10"/>
+    <sheet name="10-采购管理" sheetId="10" r:id="rId11"/>
+    <sheet name="Tips" sheetId="11" r:id="rId12"/>
     <sheet name="精炼" sheetId="12" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1378,10 +1377,6 @@
 ⑤刊登广告
 ⑥分析技术
 ⑦采购谈判</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>税金是间接成本</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1679,10 +1674,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>7 种基本质量工具：（由粗到细，有表面到根本）散布图、直方图、帕累托图、因果图、流程图、检查表和控制图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>资源平滑技术不会改变关键路径，达不到缩短工期的目标</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1911,13 +1902,6 @@
 3建设项目团队
 4管理项目团队</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>667-4343-644</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>采购过程中，工作说明书【SOW】可以随着项目的调整修改SOW</t>
   </si>
   <si>
     <r>
@@ -2117,12 +2101,48 @@
     <t>SWOT通过优势、劣势、机会和威胁角度来分析风险</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>667-4343-644</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7种基本质量工具：（由粗到细，有表面到根本）散布图、直方图、帕累托图、因果图、流程图、检查表和控制图</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>采购过程中，工作说明书【SOW】可以随着项目的调整修改SOW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>税金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是间接成本</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2312,6 +2332,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -2417,7 +2446,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2572,6 +2601,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2858,7 +2893,841 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="36"/>
+      <c r="B1" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="30">
+        <v>6</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>292</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D5" s="60"/>
+      <c r="F5" s="60"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D6" s="60"/>
+      <c r="F6" s="60"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D7" s="60"/>
+      <c r="F7" s="60"/>
+    </row>
+    <row r="8" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="31">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D9" s="52"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D10" s="52"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D11" s="52"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D12" s="52"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D13" s="52"/>
+    </row>
+    <row r="14" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="32">
+        <v>4</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D15" s="54"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D16" s="54"/>
+    </row>
+    <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="33">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="34">
+        <v>4</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E19" s="56"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E20" s="56"/>
+    </row>
+    <row r="21" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="31">
+        <v>3</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="35">
+        <v>6</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D23" s="58"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D24" s="58"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D25" s="58"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D26" s="58"/>
+    </row>
+    <row r="27" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="34">
+        <v>4</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="33">
+        <v>4</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" s="61"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D8:D13"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="F4:F7"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" style="13" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="37.625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="29.625" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23" style="14" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="14" customWidth="1"/>
+    <col min="3" max="3" width="26" style="14" customWidth="1"/>
+    <col min="4" max="4" width="54.625" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+    </row>
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="114" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D14" s="14" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B57"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="137.125" style="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2" s="38" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B3" s="38" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B4" s="38" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="38" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="38" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="38" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="40" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="41" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="38" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="38" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28" s="38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="38" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B30" s="38" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="38" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B35" s="38" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B36" s="38" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38" s="38" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39" s="38" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" s="38" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" s="38" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" s="38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43" s="38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B44" s="38" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B45" s="38" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B46" s="38" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47" s="38" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B48" s="38" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="38" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="38" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="39" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="38" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="38" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="38" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="38" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="38" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="125.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B2" s="22" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -2990,707 +3859,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F163E3-8EE0-4D1F-BCF5-4CE45E5D8A4E}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23" style="14" customWidth="1"/>
-    <col min="2" max="2" width="26.5" style="14" customWidth="1"/>
-    <col min="3" max="3" width="26" style="14" customWidth="1"/>
-    <col min="4" max="4" width="54.625" style="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-    </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="114" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D14" s="14" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBB5C2F-A290-4F16-B87E-1CE11590255A}">
-  <dimension ref="B2:B57"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="137.125" style="38" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" s="38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3" s="38" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="38" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" s="38" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="39" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="38" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" s="38" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="38" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11" s="38" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B13" s="38" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="38" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B15" s="38" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B16" s="38" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B17" s="38" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="38" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" s="38" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B20" s="38" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B21" s="40" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B22" s="41" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B23" s="38" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B24" s="38" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B25" s="38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B26" s="42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B27" s="38" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28" s="38" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B29" s="38" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B30" s="38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B31" s="38" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B32" s="38" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="38" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="38" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="38" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B36" s="38" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" s="38" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38" s="38" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="38" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="38" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="38" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="38" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43" s="38" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B44" s="38" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B45" s="38" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B46" s="38" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="38" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="38" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="38" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="39" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="38" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="38" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="38" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="38" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="38" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="38" t="s">
-        <v>314</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744D785B-7966-44AE-B509-FA00F80BC85C}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="2.375" style="30" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="15.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36"/>
-      <c r="B1" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30">
-        <v>6</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>294</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F3" s="50"/>
-    </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="60"/>
-      <c r="F5" s="60"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D6" s="60"/>
-      <c r="F6" s="60"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D7" s="60"/>
-      <c r="F7" s="60"/>
-    </row>
-    <row r="8" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="31">
-        <v>7</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>287</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D9" s="52"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D10" s="52"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D11" s="52"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D12" s="52"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D13" s="52"/>
-    </row>
-    <row r="14" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="32">
-        <v>4</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D15" s="54"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D16" s="54"/>
-    </row>
-    <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="34">
-        <v>4</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E18" s="55" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E19" s="56"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E20" s="56"/>
-    </row>
-    <row r="21" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31">
-        <v>3</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35">
-        <v>6</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="29" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D23" s="58"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D24" s="58"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D25" s="58"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D26" s="58"/>
-    </row>
-    <row r="27" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34">
-        <v>4</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33">
-        <v>4</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="D8:D13"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="F4:F7"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03009266-14FB-43A0-85E8-01A9D9BBC3CE}">
-  <dimension ref="B2:B3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="125.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B2" s="22" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4624772D-8333-4CC6-866B-85F1E1140FC3}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3807,12 +3977,12 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D19" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D20" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.2">
@@ -3829,8 +3999,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{345C1A98-0B57-4A37-A866-F2F3FC91E31C}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3963,8 +4133,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F64142-D883-4EE7-9596-C97370C9F95F}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4063,8 +4233,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA806D3-D788-406F-8D3D-1903EF473DD8}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -4113,7 +4283,7 @@
         <v>98</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="171" x14ac:dyDescent="0.2">
@@ -4130,7 +4300,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="114" x14ac:dyDescent="0.2">
@@ -4147,7 +4317,7 @@
         <v>103</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -4189,8 +4359,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5EE9BB9-5409-4629-978A-83B1D79F1EFE}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4246,7 +4416,7 @@
         <v>109</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>110</v>
@@ -4282,7 +4452,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C14" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4294,8 +4464,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7C7AEB-3421-4F51-A5AD-C7F9CF57091B}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -4377,17 +4547,17 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C13" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -4399,8 +4569,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{796D5BC7-2C97-4D9A-BC19-492395EECC53}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4492,7 +4662,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D13" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -4502,133 +4672,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89512F5-ABC6-4E96-82C1-CBE851F5CF4A}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="25" style="13" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="37.625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="29.625" style="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="185.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="57" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
-</worksheet>
 </file>
--- a/系统集成项目管理工程师/10大管理过程(输入-输出-工具-技术)汇总表.xlsx
+++ b/系统集成项目管理工程师/10大管理过程(输入-输出-工具-技术)汇总表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" firstSheet="1" activeTab="11"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="5大过程组" sheetId="13" r:id="rId1"/>
@@ -2548,6 +2548,48 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2565,48 +2607,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2943,7 +2943,7 @@
       <c r="E2" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="45" t="s">
         <v>292</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2951,7 +2951,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F3" s="50"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30">
@@ -2960,24 +2960,24 @@
       <c r="B4" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="55" t="s">
         <v>287</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="55" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="60"/>
-      <c r="F5" s="60"/>
+      <c r="D5" s="56"/>
+      <c r="F5" s="56"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="D6" s="56"/>
+      <c r="F6" s="56"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D7" s="60"/>
-      <c r="F7" s="60"/>
+      <c r="D7" s="56"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
@@ -2986,7 +2986,7 @@
       <c r="B8" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="47" t="s">
         <v>285</v>
       </c>
       <c r="F8" s="26" t="s">
@@ -2994,19 +2994,19 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D9" s="52"/>
+      <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D10" s="52"/>
+      <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D11" s="52"/>
+      <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D12" s="52"/>
+      <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D13" s="52"/>
+      <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="32">
@@ -3015,7 +3015,7 @@
       <c r="B14" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="49" t="s">
         <v>283</v>
       </c>
       <c r="F14" s="27" t="s">
@@ -3023,10 +3023,10 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D15" s="54"/>
+      <c r="D15" s="50"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D16" s="54"/>
+      <c r="D16" s="50"/>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="33">
@@ -3055,15 +3055,15 @@
       <c r="D18" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="51" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E19" s="56"/>
+      <c r="E19" s="52"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E20" s="56"/>
+      <c r="E20" s="52"/>
     </row>
     <row r="21" spans="1:7" s="26" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
@@ -3089,7 +3089,7 @@
       <c r="B22" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="53" t="s">
         <v>269</v>
       </c>
       <c r="F22" s="29" t="s">
@@ -3097,16 +3097,16 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D23" s="58"/>
+      <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D24" s="58"/>
+      <c r="D24" s="54"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D25" s="58"/>
+      <c r="D25" s="54"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D26" s="58"/>
+      <c r="D26" s="54"/>
     </row>
     <row r="27" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34">
@@ -3149,14 +3149,14 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="43" t="s">
         <v>311</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="44"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3187,14 +3187,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
@@ -3316,13 +3316,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -3742,12 +3742,12 @@
     <col min="10" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:5" s="57" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="43" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:5" s="57" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:5" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>1</v>
@@ -3871,11 +3871,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -4004,9 +4004,9 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="42.625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="44.25" style="6" customWidth="1"/>
+    <col min="2" max="2" width="47.125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="33" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4144,8 +4144,8 @@
     <col min="4" max="4" width="29.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:4" s="59" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="59" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
     <col min="6" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:5" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="46" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:5" s="60" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>1</v>
@@ -4321,7 +4321,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="61" t="s">
         <v>194</v>
       </c>
       <c r="E12" t="s">
@@ -4329,25 +4329,25 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C13" s="45"/>
+      <c r="C13" s="59"/>
       <c r="E13" s="19" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C14" s="45"/>
+      <c r="C14" s="59"/>
       <c r="E14" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C15" s="45"/>
+      <c r="C15" s="59"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C16" s="45"/>
+      <c r="C16" s="59"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C17" s="45"/>
+      <c r="C17" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4372,13 +4372,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -4480,14 +4480,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
@@ -4581,14 +4581,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
